--- a/Assets/GameResource/Excel/物资表.xlsx
+++ b/Assets/GameResource/Excel/物资表.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8082C5D2-3BF5-416C-96C3-07A529BBC447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D18BF57-E736-4E0A-8B90-FB5C6BB336EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3204" yWindow="3204" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MaterialsConfigInfo" sheetId="1" r:id="rId1"/>
-    <sheet name="MaterialsDropGroupConfigInfo" sheetId="2" r:id="rId2"/>
+    <sheet name="MaterialsInfo" sheetId="1" r:id="rId1"/>
+    <sheet name="MaterialsDropGroupInfo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -200,6 +200,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>

--- a/Assets/GameResource/Excel/物资表.xlsx
+++ b/Assets/GameResource/Excel/物资表.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D18BF57-E736-4E0A-8B90-FB5C6BB336EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7FBA32-CFD4-4625-984B-1AC6A8DC5948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3204" yWindow="3204" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-12750" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MaterialsInfo" sheetId="1" r:id="rId1"/>
-    <sheet name="MaterialsDropGroupInfo" sheetId="2" r:id="rId2"/>
+    <sheet name="SupplyInfo" sheetId="1" r:id="rId1"/>
+    <sheet name="SupplySetInfo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,154 +34,173 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>物资id</t>
   </si>
   <si>
+    <t>物资名</t>
+  </si>
+  <si>
+    <t>物资道具1</t>
+  </si>
+  <si>
+    <t>物资道具2</t>
+  </si>
+  <si>
+    <t>物资道具3</t>
+  </si>
+  <si>
+    <t>物资道具4</t>
+  </si>
+  <si>
+    <t>物资道具5</t>
+  </si>
+  <si>
+    <t>物资道具6</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Item1Num</t>
+  </si>
+  <si>
+    <t>Item2</t>
+  </si>
+  <si>
+    <t>Item2Num</t>
+  </si>
+  <si>
+    <t>Item3</t>
+  </si>
+  <si>
+    <t>Item3Num</t>
+  </si>
+  <si>
+    <t>Item4</t>
+  </si>
+  <si>
+    <t>Item4Num</t>
+  </si>
+  <si>
+    <t>Item5</t>
+  </si>
+  <si>
+    <t>Item5Num</t>
+  </si>
+  <si>
+    <t>Item6</t>
+  </si>
+  <si>
+    <t>Item6Num</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>一堆木头</t>
+  </si>
+  <si>
+    <t>50,100</t>
+  </si>
+  <si>
+    <t>一堆石头</t>
+  </si>
+  <si>
+    <t>60,150</t>
+  </si>
+  <si>
+    <t>一堆铁块</t>
+  </si>
+  <si>
+    <t>80,200</t>
+  </si>
+  <si>
+    <t>一堆布料</t>
+  </si>
+  <si>
+    <t>100,250</t>
+  </si>
+  <si>
+    <t>一个包裹</t>
+  </si>
+  <si>
+    <t>掉落id</t>
+  </si>
+  <si>
+    <t>掉落组id</t>
+  </si>
+  <si>
+    <t>物资名字</t>
+  </si>
+  <si>
+    <t>DropId</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SupplyId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SupplyName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DroupSetId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>难度</t>
-  </si>
-  <si>
-    <t>物资名</t>
-  </si>
-  <si>
-    <t>物资道具1</t>
-  </si>
-  <si>
-    <t>物资道具1数量</t>
-  </si>
-  <si>
-    <t>物资道具2</t>
-  </si>
-  <si>
-    <t>物资道具2数量</t>
-  </si>
-  <si>
-    <t>物资道具3</t>
-  </si>
-  <si>
-    <t>物资道具3数量</t>
-  </si>
-  <si>
-    <t>物资道具4</t>
-  </si>
-  <si>
-    <t>物资道具4数量</t>
-  </si>
-  <si>
-    <t>物资道具5</t>
-  </si>
-  <si>
-    <t>物资道具5数量</t>
-  </si>
-  <si>
-    <t>物资道具6</t>
-  </si>
-  <si>
-    <t>物资道具6数量</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Stage</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Item1Num</t>
-  </si>
-  <si>
-    <t>Item2</t>
-  </si>
-  <si>
-    <t>Item2Num</t>
-  </si>
-  <si>
-    <t>Item3</t>
-  </si>
-  <si>
-    <t>Item3Num</t>
-  </si>
-  <si>
-    <t>Item4</t>
-  </si>
-  <si>
-    <t>Item4Num</t>
-  </si>
-  <si>
-    <t>Item5</t>
-  </si>
-  <si>
-    <t>Item5Num</t>
-  </si>
-  <si>
-    <t>Item6</t>
-  </si>
-  <si>
-    <t>Item6Num</t>
-  </si>
-  <si>
-    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一堆布料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>一堆木头</t>
-  </si>
-  <si>
-    <t>50,100</t>
-  </si>
-  <si>
-    <t>一堆石头</t>
-  </si>
-  <si>
-    <t>60,150</t>
-  </si>
-  <si>
-    <t>一堆铁块</t>
-  </si>
-  <si>
-    <t>80,200</t>
-  </si>
-  <si>
-    <t>一堆布料</t>
-  </si>
-  <si>
-    <t>100,250</t>
-  </si>
-  <si>
-    <t>一个包裹</t>
-  </si>
-  <si>
-    <t>掉落id</t>
-  </si>
-  <si>
-    <t>掉落组id</t>
-  </si>
-  <si>
-    <t>物资名字</t>
-  </si>
-  <si>
-    <t>DropId</t>
-  </si>
-  <si>
-    <t>DroupGroupId</t>
-  </si>
-  <si>
-    <t>MaterialsId</t>
-  </si>
-  <si>
-    <t>MaterialsName</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资道具1掉落范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资道具2掉落范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资道具3
+掉落范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资道具4掉落范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资道具5掉落范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物资道具6掉落范围</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -235,12 +254,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -513,158 +541,158 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.5546875" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" customWidth="1"/>
     <col min="6" max="6" width="10.88671875" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" customWidth="1"/>
     <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="15.109375" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" customWidth="1"/>
     <col min="14" max="14" width="9.88671875" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="K1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="O1" t="s">
         <v>21</v>
-      </c>
-      <c r="I1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="J3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" t="s">
+      <c r="K3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" t="s">
+      <c r="M3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" t="s">
-        <v>14</v>
+      <c r="O3" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -675,13 +703,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -692,13 +720,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -709,13 +737,13 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -726,13 +754,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -743,31 +771,31 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8">
         <v>2</v>
       </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8">
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8">
         <v>3</v>
       </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8">
+      <c r="I8" s="2">
+        <v>50100</v>
+      </c>
+      <c r="J8">
         <v>4</v>
       </c>
-      <c r="I8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-      <c r="K8" t="s">
-        <v>32</v>
+      <c r="K8" s="2">
+        <v>50100</v>
       </c>
     </row>
   </sheetData>
@@ -790,44 +818,44 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -841,7 +869,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -855,7 +883,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -869,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,8 +910,8 @@
       <c r="C7">
         <v>4</v>
       </c>
-      <c r="D7" t="s">
-        <v>37</v>
+      <c r="D7" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameResource/Excel/物资表.xlsx
+++ b/Assets/GameResource/Excel/物资表.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7FBA32-CFD4-4625-984B-1AC6A8DC5948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12750" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SupplyInfo" sheetId="1" r:id="rId1"/>

--- a/Assets/GameResource/Excel/物资表.xlsx
+++ b/Assets/GameResource/Excel/物资表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7FBA32-CFD4-4625-984B-1AC6A8DC5948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C951E6A9-7E7D-4DA9-BEE3-4F1675FC276B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="52">
   <si>
     <t>物资id</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>一堆铁块</t>
-  </si>
-  <si>
-    <t>80,200</t>
   </si>
   <si>
     <t>一堆布料</t>
@@ -201,6 +198,14 @@
   </si>
   <si>
     <t>物资道具6掉落范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80,200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -254,14 +259,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -269,6 +271,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,13 +552,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.5546875" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" style="4" customWidth="1"/>
     <col min="6" max="6" width="10.88671875" customWidth="1"/>
     <col min="7" max="7" width="10.21875" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" style="4" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" style="4" customWidth="1"/>
     <col min="12" max="12" width="11.5546875" customWidth="1"/>
     <col min="13" max="13" width="10.77734375" customWidth="1"/>
     <col min="14" max="14" width="9.88671875" customWidth="1"/>
@@ -565,9 +576,9 @@
         <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F1" t="s">
@@ -579,13 +590,13 @@
       <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L1" t="s">
@@ -606,7 +617,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -614,25 +625,25 @@
       <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L2" t="s">
@@ -648,51 +659,51 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="3" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:15" s="2" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -708,8 +719,8 @@
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>25</v>
+      <c r="E4" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -725,7 +736,7 @@
       <c r="D5">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>27</v>
       </c>
     </row>
@@ -742,8 +753,8 @@
       <c r="D6">
         <v>3</v>
       </c>
-      <c r="E6" t="s">
-        <v>29</v>
+      <c r="E6" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -754,13 +765,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" t="s">
-        <v>31</v>
+      <c r="E7" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -771,12 +782,12 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="F8">
@@ -788,14 +799,14 @@
       <c r="H8">
         <v>3</v>
       </c>
-      <c r="I8" s="2">
-        <v>50100</v>
+      <c r="I8" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
-      <c r="K8" s="2">
-        <v>50100</v>
+      <c r="K8" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -818,16 +829,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -846,16 +857,16 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -911,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
